--- a/data/bulk_task_creation_valid.xlsx
+++ b/data/bulk_task_creation_valid.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="38">
   <si>
     <t>Task Name*</t>
   </si>
@@ -133,10 +133,10 @@
     <t>Text (Max 40 characters)</t>
   </si>
   <si>
-    <t>Check Bulk Creation</t>
-  </si>
-  <si>
     <t>Only once</t>
+  </si>
+  <si>
+    <t>Bulk Task Creation</t>
   </si>
 </sst>
 </file>
@@ -681,45 +681,29 @@
     </row>
     <row r="3" spans="1:21">
       <c r="A3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="3">
+        <v>46211</v>
+      </c>
+      <c r="C3" s="3">
+        <v>46211</v>
+      </c>
+      <c r="K3" t="s">
         <v>36</v>
-      </c>
-      <c r="B3" s="3">
-        <v>46203</v>
-      </c>
-      <c r="C3" s="3">
-        <v>46203</v>
-      </c>
-      <c r="K3" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:21">
-      <c r="A4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="3">
-        <v>46203</v>
-      </c>
-      <c r="C4" s="3">
-        <v>46203</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="A4" s="4"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="K4" s="1"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="3">
-        <v>46203</v>
-      </c>
-      <c r="C5" s="3">
-        <v>46203</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="A5" s="4"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="K5" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/bulk_task_creation_valid.xlsx
+++ b/data/bulk_task_creation_valid.xlsx
@@ -684,10 +684,10 @@
         <v>37</v>
       </c>
       <c r="B3" s="3">
-        <v>46211</v>
+        <v>46225</v>
       </c>
       <c r="C3" s="3">
-        <v>46211</v>
+        <v>46225</v>
       </c>
       <c r="K3" t="s">
         <v>36</v>
